--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-type-organisation.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-type-organisation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FR Core CodeSystem Types d'Organisations</t>
+    <t>FR Core CodeSystem Organization Type</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This is an example code system that includes all the InteropSanté Organizations types codes.</t>
+    <t>Organization type</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -585,7 +585,9 @@
       <c r="C2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -597,7 +599,9 @@
       <c r="C3" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -609,7 +613,9 @@
       <c r="C4" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>47</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -621,7 +627,9 @@
       <c r="C5" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -633,7 +641,9 @@
       <c r="C6" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -645,7 +655,9 @@
       <c r="C7" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -657,7 +669,9 @@
       <c r="C8" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -669,7 +683,9 @@
       <c r="C9" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -681,7 +697,9 @@
       <c r="C10" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>59</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -693,7 +711,9 @@
       <c r="C11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -705,7 +725,9 @@
       <c r="C12" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -717,7 +739,9 @@
       <c r="C13" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>65</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -729,7 +753,9 @@
       <c r="C14" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>67</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -741,7 +767,9 @@
       <c r="C15" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -753,7 +781,9 @@
       <c r="C16" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -765,7 +795,9 @@
       <c r="C17" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -777,7 +809,9 @@
       <c r="C18" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-type-organisation.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-type-organisation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FR Core CodeSystem Organization Type</t>
+    <t>FR Core CodeSystem Types d'Organisations</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Organization type</t>
+    <t>This is an example code system that includes all the InteropSanté Organizations types codes.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -585,9 +585,7 @@
       <c r="C2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>43</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -599,9 +597,7 @@
       <c r="C3" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>45</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -613,9 +609,7 @@
       <c r="C4" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>47</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -627,9 +621,7 @@
       <c r="C5" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>49</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -641,9 +633,7 @@
       <c r="C6" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>51</v>
-      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -655,9 +645,7 @@
       <c r="C7" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>53</v>
-      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -669,9 +657,7 @@
       <c r="C8" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>55</v>
-      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -683,9 +669,7 @@
       <c r="C9" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>57</v>
-      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -697,9 +681,7 @@
       <c r="C10" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>59</v>
-      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -711,9 +693,7 @@
       <c r="C11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>61</v>
-      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -725,9 +705,7 @@
       <c r="C12" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="D12" t="s" s="2">
-        <v>63</v>
-      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -739,9 +717,7 @@
       <c r="C13" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="D13" t="s" s="2">
-        <v>65</v>
-      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -753,9 +729,7 @@
       <c r="C14" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="D14" t="s" s="2">
-        <v>67</v>
-      </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -767,9 +741,7 @@
       <c r="C15" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="D15" t="s" s="2">
-        <v>69</v>
-      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -781,9 +753,7 @@
       <c r="C16" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="D16" t="s" s="2">
-        <v>71</v>
-      </c>
+      <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -795,9 +765,7 @@
       <c r="C17" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="D17" t="s" s="2">
-        <v>73</v>
-      </c>
+      <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -809,9 +777,7 @@
       <c r="C18" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="D18" t="s" s="2">
-        <v>75</v>
-      </c>
+      <c r="D18" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-type-organisation.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-type-organisation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FR Core CodeSystem Types d'Organisations</t>
+    <t>FR Core CodeSystem Organization Type</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This is an example code system that includes all the InteropSanté Organizations types codes.</t>
+    <t>Organization type</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -585,7 +585,9 @@
       <c r="C2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -597,7 +599,9 @@
       <c r="C3" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -609,7 +613,9 @@
       <c r="C4" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>47</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -621,7 +627,9 @@
       <c r="C5" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -633,7 +641,9 @@
       <c r="C6" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -645,7 +655,9 @@
       <c r="C7" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -657,7 +669,9 @@
       <c r="C8" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -669,7 +683,9 @@
       <c r="C9" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -681,7 +697,9 @@
       <c r="C10" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>59</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -693,7 +711,9 @@
       <c r="C11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -705,7 +725,9 @@
       <c r="C12" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -717,7 +739,9 @@
       <c r="C13" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>65</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -729,7 +753,9 @@
       <c r="C14" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>67</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -741,7 +767,9 @@
       <c r="C15" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -753,7 +781,9 @@
       <c r="C16" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -765,7 +795,9 @@
       <c r="C17" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -777,7 +809,9 @@
       <c r="C18" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
